--- a/SNTL_APIList.xlsx
+++ b/SNTL_APIList.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="권한범례" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API목록'!$A$3:$I$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API목록'!$A$3:$I$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -70,7 +70,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -192,6 +192,26 @@
         <fgColor rgb="00D6E4BC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B8CCE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2DCDB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -217,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -336,6 +356,33 @@
     <xf numFmtId="0" fontId="5" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -373,6 +420,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -742,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -766,7 +828,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>총 143개 API | 최종 업데이트: 2026-04-16</t>
+          <t>총 183개 API | 최종 업데이트: 2026-04-16</t>
         </is>
       </c>
     </row>
@@ -7538,8 +7600,1888 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="29" t="inlineStr">
+        <is>
+          <t>API-FR01</t>
+        </is>
+      </c>
+      <c r="B147" s="30" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>/fare-rates/individual</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>개인회원 등급별 운임요율 목록</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>회원등급(BASIC/SILVER/GOLD/VIP)별 운임요율(%) 목록</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H147" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="29" t="inlineStr">
+        <is>
+          <t>API-FR02</t>
+        </is>
+      </c>
+      <c r="B148" s="30" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>/fare-rates/individual</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>개인회원 운임요율 등록</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>등급별 운임요율 등록</t>
+        </is>
+      </c>
+      <c r="G148" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H148" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="29" t="inlineStr">
+        <is>
+          <t>API-FR03</t>
+        </is>
+      </c>
+      <c r="B149" s="30" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>/fare-rates/individual/{rateId}</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>개인회원 운임요율 수정</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>운임요율 수정</t>
+        </is>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H149" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="29" t="inlineStr">
+        <is>
+          <t>API-FR04</t>
+        </is>
+      </c>
+      <c r="B150" s="30" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="C150" s="16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>/fare-rates/individual/{rateId}</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>개인회원 운임요율 삭제</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="inlineStr">
+        <is>
+          <t>운임요율 삭제</t>
+        </is>
+      </c>
+      <c r="G150" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H150" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="29" t="inlineStr">
+        <is>
+          <t>API-FR05</t>
+        </is>
+      </c>
+      <c r="B151" s="30" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="C151" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>/fare-rates/corporate</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>법인회원별 운임요율 목록</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>법인ID별 운임요율 목록</t>
+        </is>
+      </c>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="29" t="inlineStr">
+        <is>
+          <t>API-FR06</t>
+        </is>
+      </c>
+      <c r="B152" s="30" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>/fare-rates/corporate</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>법인회원 운임요율 등록</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>법인별 운임요율 등록</t>
+        </is>
+      </c>
+      <c r="G152" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="29" t="inlineStr">
+        <is>
+          <t>API-FR07</t>
+        </is>
+      </c>
+      <c r="B153" s="30" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>/fare-rates/corporate/{rateId}</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>법인회원 운임요율 수정</t>
+        </is>
+      </c>
+      <c r="F153" s="8" t="inlineStr">
+        <is>
+          <t>운임요율 수정</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H153" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="29" t="inlineStr">
+        <is>
+          <t>API-FR08</t>
+        </is>
+      </c>
+      <c r="B154" s="30" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>/fare-rates/corporate/{rateId}</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>법인회원 운임요율 삭제</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="inlineStr">
+        <is>
+          <t>운임요율 삭제</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="40" t="inlineStr">
+        <is>
+          <t>API-EX01</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="C155" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>/exchange-rates</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>환율 조회</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>서울외국환중개소 기준환율. 로그인 국가코드 기준</t>
+        </is>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="40" t="inlineStr">
+        <is>
+          <t>API-EX02</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>/exchange-rates/sync</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>환율 연계</t>
+        </is>
+      </c>
+      <c r="F156" s="8" t="inlineStr">
+        <is>
+          <t>서울외국환중개소 API 호출, 영업일 오전 8시 자동 갱신</t>
+        </is>
+      </c>
+      <c r="G156" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H156" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="41" t="inlineStr">
+        <is>
+          <t>API-AT01</t>
+        </is>
+      </c>
+      <c r="B157" s="42" t="inlineStr">
+        <is>
+          <t>항공운송수단</t>
+        </is>
+      </c>
+      <c r="C157" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>/transports/air</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>항공운송수단 목록</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="inlineStr">
+        <is>
+          <t>출발/도착 공항코드로 조회</t>
+        </is>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H157" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I157" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="41" t="inlineStr">
+        <is>
+          <t>API-AT02</t>
+        </is>
+      </c>
+      <c r="B158" s="42" t="inlineStr">
+        <is>
+          <t>항공운송수단</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>/transports/air</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>항공운송수단 등록</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>출발/도착 공항코드+항공편명 등록</t>
+        </is>
+      </c>
+      <c r="G158" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H158" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I158" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="41" t="inlineStr">
+        <is>
+          <t>API-AT03</t>
+        </is>
+      </c>
+      <c r="B159" s="42" t="inlineStr">
+        <is>
+          <t>항공운송수단</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>/transports/air/{transportId}</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>항공운송수단 수정</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>항공편명 수정</t>
+        </is>
+      </c>
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H159" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="41" t="inlineStr">
+        <is>
+          <t>API-AT04</t>
+        </is>
+      </c>
+      <c r="B160" s="42" t="inlineStr">
+        <is>
+          <t>항공운송수단</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>/transports/air/{transportId}</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>항공운송수단 삭제</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>운송원가 연결 시 삭제 불가</t>
+        </is>
+      </c>
+      <c r="G160" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H160" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I160" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="41" t="inlineStr">
+        <is>
+          <t>API-AT05</t>
+        </is>
+      </c>
+      <c r="B161" s="42" t="inlineStr">
+        <is>
+          <t>항공운송수단</t>
+        </is>
+      </c>
+      <c r="C161" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>/transports/air/{transportId}/costs</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>항공 운송원가 조회</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="inlineStr">
+        <is>
+          <t>부피/중량기준 운송원가 조회</t>
+        </is>
+      </c>
+      <c r="G161" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H161" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I161" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="41" t="inlineStr">
+        <is>
+          <t>API-AT06</t>
+        </is>
+      </c>
+      <c r="B162" s="42" t="inlineStr">
+        <is>
+          <t>항공운송수단</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>/transports/air/{transportId}/costs</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>항공 운송원가 등록</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>부피기준(X·Y·Z·USD) 또는 중량기준(Kg·USD)</t>
+        </is>
+      </c>
+      <c r="G162" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H162" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I162" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="41" t="inlineStr">
+        <is>
+          <t>API-AT07</t>
+        </is>
+      </c>
+      <c r="B163" s="42" t="inlineStr">
+        <is>
+          <t>항공운송수단</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>/transports/air/{transportId}/costs/{costId}</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>항공 운송원가 수정</t>
+        </is>
+      </c>
+      <c r="F163" s="8" t="inlineStr">
+        <is>
+          <t>운송원가(USD) 수정</t>
+        </is>
+      </c>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H163" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I163" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="43" t="inlineStr">
+        <is>
+          <t>API-ST01</t>
+        </is>
+      </c>
+      <c r="B164" s="44" t="inlineStr">
+        <is>
+          <t>해운운송수단</t>
+        </is>
+      </c>
+      <c r="C164" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>/transports/sea</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>해운운송수단 목록</t>
+        </is>
+      </c>
+      <c r="F164" s="8" t="inlineStr">
+        <is>
+          <t>출발/도착 항구코드로 조회</t>
+        </is>
+      </c>
+      <c r="G164" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H164" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I164" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="43" t="inlineStr">
+        <is>
+          <t>API-ST02</t>
+        </is>
+      </c>
+      <c r="B165" s="44" t="inlineStr">
+        <is>
+          <t>해운운송수단</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>/transports/sea</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>해운운송수단 등록</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>출발/도착 항구코드+해운편명 등록</t>
+        </is>
+      </c>
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H165" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="43" t="inlineStr">
+        <is>
+          <t>API-ST03</t>
+        </is>
+      </c>
+      <c r="B166" s="44" t="inlineStr">
+        <is>
+          <t>해운운송수단</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>/transports/sea/{transportId}</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>해운운송수단 수정</t>
+        </is>
+      </c>
+      <c r="F166" s="8" t="inlineStr">
+        <is>
+          <t>해운편명 수정</t>
+        </is>
+      </c>
+      <c r="G166" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H166" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="43" t="inlineStr">
+        <is>
+          <t>API-ST04</t>
+        </is>
+      </c>
+      <c r="B167" s="44" t="inlineStr">
+        <is>
+          <t>해운운송수단</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>/transports/sea/{transportId}</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>해운운송수단 삭제</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>운송원가 연결 시 삭제 불가</t>
+        </is>
+      </c>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="43" t="inlineStr">
+        <is>
+          <t>API-ST05</t>
+        </is>
+      </c>
+      <c r="B168" s="44" t="inlineStr">
+        <is>
+          <t>해운운송수단</t>
+        </is>
+      </c>
+      <c r="C168" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>/transports/sea/{transportId}/costs</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>해운 운송원가 조회</t>
+        </is>
+      </c>
+      <c r="F168" s="8" t="inlineStr">
+        <is>
+          <t>부피/중량기준 운송원가 조회</t>
+        </is>
+      </c>
+      <c r="G168" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H168" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I168" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="43" t="inlineStr">
+        <is>
+          <t>API-ST06</t>
+        </is>
+      </c>
+      <c r="B169" s="44" t="inlineStr">
+        <is>
+          <t>해운운송수단</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>/transports/sea/{transportId}/costs</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>해운 운송원가 등록</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>부피기준(X·Y·Z·USD) 또는 중량기준(Kg·USD)</t>
+        </is>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H169" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="43" t="inlineStr">
+        <is>
+          <t>API-ST07</t>
+        </is>
+      </c>
+      <c r="B170" s="44" t="inlineStr">
+        <is>
+          <t>해운운송수단</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>/transports/sea/{transportId}/costs/{costId}</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>해운 운송원가 수정</t>
+        </is>
+      </c>
+      <c r="F170" s="8" t="inlineStr">
+        <is>
+          <t>운송원가(USD) 수정</t>
+        </is>
+      </c>
+      <c r="G170" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H170" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I170" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="45" t="inlineStr">
+        <is>
+          <t>API-CB01</t>
+        </is>
+      </c>
+      <c r="B171" s="46" t="inlineStr">
+        <is>
+          <t>통관사</t>
+        </is>
+      </c>
+      <c r="C171" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>/customs-brokers</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>통관사 목록</t>
+        </is>
+      </c>
+      <c r="F171" s="8" t="inlineStr">
+        <is>
+          <t>국가코드·운송구분·입항코드로 조회</t>
+        </is>
+      </c>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H171" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I171" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="45" t="inlineStr">
+        <is>
+          <t>API-CB02</t>
+        </is>
+      </c>
+      <c r="B172" s="46" t="inlineStr">
+        <is>
+          <t>통관사</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>/customs-brokers</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>통관사 등록</t>
+        </is>
+      </c>
+      <c r="F172" s="8" t="inlineStr">
+        <is>
+          <t>국가코드+서비스구분(AIR/SEA)+입항코드+API연동여부</t>
+        </is>
+      </c>
+      <c r="G172" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H172" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I172" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="45" t="inlineStr">
+        <is>
+          <t>API-CB03</t>
+        </is>
+      </c>
+      <c r="B173" s="46" t="inlineStr">
+        <is>
+          <t>통관사</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>/customs-brokers/{brokerId}</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>통관사 수정</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>통관사 정보 수정</t>
+        </is>
+      </c>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H173" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I173" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="45" t="inlineStr">
+        <is>
+          <t>API-CB04</t>
+        </is>
+      </c>
+      <c r="B174" s="46" t="inlineStr">
+        <is>
+          <t>통관사</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>/customs-brokers/{brokerId}</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>통관사 삭제</t>
+        </is>
+      </c>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>통관원가 연결 시 삭제 불가</t>
+        </is>
+      </c>
+      <c r="G174" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H174" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="45" t="inlineStr">
+        <is>
+          <t>API-CB05</t>
+        </is>
+      </c>
+      <c r="B175" s="46" t="inlineStr">
+        <is>
+          <t>통관사</t>
+        </is>
+      </c>
+      <c r="C175" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>/customs-brokers/{brokerId}/costs</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>통관원가 조회</t>
+        </is>
+      </c>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>부피/중량기준 통관원가 조회</t>
+        </is>
+      </c>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H175" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I175" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="45" t="inlineStr">
+        <is>
+          <t>API-CB06</t>
+        </is>
+      </c>
+      <c r="B176" s="46" t="inlineStr">
+        <is>
+          <t>통관사</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>/customs-brokers/{brokerId}/costs</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>통관원가 등록</t>
+        </is>
+      </c>
+      <c r="F176" s="8" t="inlineStr">
+        <is>
+          <t>부피기준(X·Y·Z·USD) 또는 중량기준(Kg·USD)</t>
+        </is>
+      </c>
+      <c r="G176" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I176" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="45" t="inlineStr">
+        <is>
+          <t>API-CB07</t>
+        </is>
+      </c>
+      <c r="B177" s="46" t="inlineStr">
+        <is>
+          <t>통관사</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>/customs-brokers/{brokerId}/costs/{costId}</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>통관원가 수정</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>통관원가(USD) 수정</t>
+        </is>
+      </c>
+      <c r="G177" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H177" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I177" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="47" t="inlineStr">
+        <is>
+          <t>API-CW01</t>
+        </is>
+      </c>
+      <c r="B178" s="48" t="inlineStr">
+        <is>
+          <t>택배배송장</t>
+        </is>
+      </c>
+      <c r="C178" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>/codes/couriers/{courierId}/waybills</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>택배배송장 목록</t>
+        </is>
+      </c>
+      <c r="F178" s="8" t="inlineStr">
+        <is>
+          <t>국가코드·택배사명으로 조회</t>
+        </is>
+      </c>
+      <c r="G178" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H178" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I178" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="47" t="inlineStr">
+        <is>
+          <t>API-CW02</t>
+        </is>
+      </c>
+      <c r="B179" s="48" t="inlineStr">
+        <is>
+          <t>택배배송장</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>/codes/couriers/{courierId}/waybills</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>택배배송장 등록</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>국가코드+배송장 양식파일(BLOB) 등록</t>
+        </is>
+      </c>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H179" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="47" t="inlineStr">
+        <is>
+          <t>API-CW03</t>
+        </is>
+      </c>
+      <c r="B180" s="48" t="inlineStr">
+        <is>
+          <t>택배배송장</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>/codes/couriers/{courierId}/waybills/{waybillId}</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>택배배송장 수정</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>배송장 양식파일 수정</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H180" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I180" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="47" t="inlineStr">
+        <is>
+          <t>API-CW04</t>
+        </is>
+      </c>
+      <c r="B181" s="48" t="inlineStr">
+        <is>
+          <t>택배배송장</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>/codes/couriers/{courierId}/waybills/{waybillId}</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>택배배송장 삭제</t>
+        </is>
+      </c>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>배송장 삭제</t>
+        </is>
+      </c>
+      <c r="G181" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H181" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="I181" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="24" t="inlineStr">
+        <is>
+          <t>API-PP01</t>
+        </is>
+      </c>
+      <c r="B182" s="25" t="inlineStr">
+        <is>
+          <t>선불금</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>/prepaid/balance</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>선불금 잔액 조회 (본인)</t>
+        </is>
+      </c>
+      <c r="F182" s="8" t="inlineStr">
+        <is>
+          <t>본인 선불금 잔액 조회</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H182" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="I182" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="24" t="inlineStr">
+        <is>
+          <t>API-PP02</t>
+        </is>
+      </c>
+      <c r="B183" s="25" t="inlineStr">
+        <is>
+          <t>선불금</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>/prepaid/charge-request</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>선불금 충전 요청</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>입금 후 충전 금액 입력, 관리자 확인 요청</t>
+        </is>
+      </c>
+      <c r="G183" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H183" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="24" t="inlineStr">
+        <is>
+          <t>API-PP03</t>
+        </is>
+      </c>
+      <c r="B184" s="25" t="inlineStr">
+        <is>
+          <t>선불금</t>
+        </is>
+      </c>
+      <c r="C184" s="17" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>/prepaid/charge-requests/{requestId}/confirm</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>충전 확인 (관리자)</t>
+        </is>
+      </c>
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>실제 입금 확인 후 최종 충전 처리, 잔액 반영</t>
+        </is>
+      </c>
+      <c r="G184" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H184" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I184" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="24" t="inlineStr">
+        <is>
+          <t>API-PP04</t>
+        </is>
+      </c>
+      <c r="B185" s="25" t="inlineStr">
+        <is>
+          <t>선불금</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>/prepaid/refund-request</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>환불 요청</t>
+        </is>
+      </c>
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>미사용 잔액 환불 요청, 환불 계좌정보 입력</t>
+        </is>
+      </c>
+      <c r="G185" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H185" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="I185" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="24" t="inlineStr">
+        <is>
+          <t>API-PP05</t>
+        </is>
+      </c>
+      <c r="B186" s="25" t="inlineStr">
+        <is>
+          <t>선불금</t>
+        </is>
+      </c>
+      <c r="C186" s="15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>/prepaid/admin/balances</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>전체 선불금 조회 (관리자)</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>회원별·법인별 선불금 잔액 전체 조회</t>
+        </is>
+      </c>
+      <c r="G186" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H186" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN/OPR</t>
+        </is>
+      </c>
+      <c r="I186" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I146"/>
+  <autoFilter ref="A3:I186"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -7554,7 +9496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7564,7 +9506,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>도메인별 API 통계</t>
         </is>
@@ -7593,7 +9535,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
@@ -7613,7 +9555,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>회원-개인</t>
         </is>
@@ -7633,7 +9575,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>회원-법인</t>
         </is>
@@ -7653,7 +9595,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>회원-담당자</t>
         </is>
@@ -7673,7 +9615,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>회원-부서</t>
         </is>
@@ -7693,7 +9635,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>회원-등급</t>
         </is>
@@ -7713,7 +9655,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>오더</t>
         </is>
@@ -7733,7 +9675,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>마스터오더</t>
         </is>
@@ -7753,7 +9695,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>창고</t>
         </is>
@@ -7773,7 +9715,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>Tracking</t>
         </is>
@@ -7793,7 +9735,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>회계/청구</t>
         </is>
@@ -7813,7 +9755,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t>원가</t>
         </is>
@@ -7833,7 +9775,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
@@ -7853,7 +9795,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>VOC</t>
         </is>
@@ -7873,7 +9815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
@@ -7893,7 +9835,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="52" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>기준코드</t>
         </is>
@@ -7913,16 +9855,128 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr">
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>운임요율</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="62" t="inlineStr">
+        <is>
+          <t>환율</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="inlineStr">
+        <is>
+          <t>항공운송수단</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="64" t="inlineStr">
+        <is>
+          <t>해운운송수단</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="65" t="inlineStr">
+        <is>
+          <t>통관사</t>
+        </is>
+      </c>
+      <c r="B23" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="66" t="inlineStr">
+        <is>
+          <t>택배배송장</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t>선불금</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="67" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="54" t="n"/>
+      <c r="B26" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="C26" s="68" t="n"/>
+      <c r="D26" s="68" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7947,7 +10001,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>권한 코드 범례</t>
         </is>
